--- a/img/Caso_hotel.xlsx
+++ b/img/Caso_hotel.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="4" documentId="11_41A4F3D452EC416D8DFAB4C4A571E8D08186B5E7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0D38313-DF0C-4A8D-A6C7-7B7517DEB914}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="781" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5160" yWindow="0" windowWidth="13824" windowHeight="7536" tabRatio="781" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guía" sheetId="1" r:id="rId1"/>
@@ -1934,58 +1934,20 @@
   </cellStyleXfs>
   <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2066,6 +2028,47 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2074,9 +2077,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2164,6 +2164,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2354,188 +2358,188 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
     </row>
     <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
     </row>
     <row r="20" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
+      <c r="A20" s="39"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
+      <c r="A21" s="39"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
+      <c r="A22" s="39"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2561,425 +2565,455 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
     </row>
     <row r="4" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
     </row>
     <row r="6" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
     </row>
     <row r="7" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
     </row>
     <row r="8" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
     </row>
     <row r="9" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
     </row>
     <row r="10" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
     </row>
     <row r="11" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
     </row>
     <row r="12" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
     </row>
     <row r="13" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
     </row>
     <row r="14" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
     </row>
     <row r="15" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
     </row>
     <row r="17" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
     </row>
     <row r="19" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
     </row>
     <row r="20" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
     </row>
     <row r="22" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
     </row>
     <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
     </row>
     <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
     </row>
     <row r="25" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
     </row>
     <row r="27" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44"/>
     </row>
     <row r="29" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="43"/>
     </row>
     <row r="30" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
     </row>
     <row r="31" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
     </row>
     <row r="32" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
     </row>
     <row r="34" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
     </row>
     <row r="35" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
+      <c r="B35" s="41"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
     </row>
     <row r="36" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
+      <c r="B36" s="41"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="41"/>
     </row>
     <row r="37" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
+      <c r="B37" s="41"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
     </row>
     <row r="39" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="9" t="s">
+      <c r="A39" s="42" t="s">
         <v>78</v>
       </c>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
+      <c r="B39" s="42"/>
+      <c r="C39" s="42"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="42"/>
+      <c r="F39" s="42"/>
     </row>
     <row r="40" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
+      <c r="B40" s="41"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="41"/>
+      <c r="F40" s="41"/>
     </row>
     <row r="42" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="42" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
+      <c r="B42" s="42"/>
+      <c r="C42" s="42"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
     </row>
     <row r="43" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="41"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="41"/>
     </row>
     <row r="44" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
+      <c r="B44" s="41"/>
+      <c r="C44" s="41"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="41"/>
+      <c r="F44" s="41"/>
     </row>
     <row r="45" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
+      <c r="B45" s="41"/>
+      <c r="C45" s="41"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="41"/>
     </row>
     <row r="46" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
+      <c r="B46" s="41"/>
+      <c r="C46" s="41"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="41"/>
     </row>
     <row r="48" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="9" t="s">
+      <c r="A48" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
+      <c r="B48" s="42"/>
+      <c r="C48" s="42"/>
+      <c r="D48" s="42"/>
+      <c r="E48" s="42"/>
+      <c r="F48" s="42"/>
     </row>
     <row r="49" spans="1:6" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
+      <c r="B49" s="41"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A37:F37"/>
     <mergeCell ref="A45:F45"/>
     <mergeCell ref="A46:F46"/>
     <mergeCell ref="A48:F48"/>
@@ -2989,36 +3023,6 @@
     <mergeCell ref="A42:F42"/>
     <mergeCell ref="A43:F43"/>
     <mergeCell ref="A44:F44"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="B7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3040,534 +3044,534 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="H4" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="24">
+      <c r="A5" s="10">
         <v>1</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="10">
         <v>5</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="G5" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="H5" s="26" t="s">
+      <c r="H5" s="12" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="24">
+      <c r="A6" s="10">
         <v>2</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="10">
         <v>5</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="26" t="s">
+      <c r="H6" s="12" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="24">
+      <c r="A7" s="10">
         <v>3</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="10">
         <v>5</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="H7" s="26" t="s">
+      <c r="H7" s="12" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="24">
+      <c r="A8" s="10">
         <v>4</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24" t="s">
+      <c r="D8" s="10"/>
+      <c r="E8" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="H8" s="26" t="s">
+      <c r="H8" s="12" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="24">
+      <c r="A9" s="10">
         <v>5</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="10">
         <v>3</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="H9" s="27" t="s">
+      <c r="H9" s="13" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="24">
+      <c r="A10" s="10">
         <v>6</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="10">
         <v>2</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G10" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="H10" s="28" t="s">
+      <c r="H10" s="14" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="24">
+      <c r="A11" s="10">
         <v>7</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="10">
         <v>2</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="H11" s="28" t="s">
+      <c r="H11" s="14" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="24">
+      <c r="A12" s="10">
         <v>8</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="10">
         <v>3</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="H12" s="27" t="s">
+      <c r="H12" s="13" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="24">
+      <c r="A13" s="10">
         <v>9</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24" t="s">
+      <c r="D13" s="10"/>
+      <c r="E13" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="F13" s="17" t="s">
+      <c r="F13" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="H13" s="28" t="s">
+      <c r="H13" s="14" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="24">
+      <c r="A14" s="10">
         <v>10</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="10">
         <v>4</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="H14" s="27" t="s">
+      <c r="H14" s="13" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="24">
+      <c r="A15" s="10">
         <v>11</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="10">
         <v>2</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="F15" s="17" t="s">
+      <c r="F15" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="H15" s="28" t="s">
+      <c r="H15" s="14" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="24">
+      <c r="A16" s="10">
         <v>12</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="10">
         <v>3</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="F16" s="17" t="s">
+      <c r="F16" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G16" s="25" t="s">
+      <c r="G16" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="H16" s="27" t="s">
+      <c r="H16" s="13" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="24">
+      <c r="A17" s="10">
         <v>13</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="10">
         <v>5</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="F17" s="17" t="s">
+      <c r="F17" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="G17" s="25" t="s">
+      <c r="G17" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="H17" s="26" t="s">
+      <c r="H17" s="12" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="39" t="s">
         <v>143</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
     </row>
     <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="4" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
     </row>
     <row r="25" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="E25" s="16" t="s">
+      <c r="E25" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A26" s="17">
+      <c r="A26" s="2">
         <v>1</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="15">
         <f>AVERAGE('Respuestas Encuesta'!D6:D55)</f>
         <v>8.06</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="2" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="66" x14ac:dyDescent="0.3">
-      <c r="A27" s="17">
+      <c r="A27" s="2">
         <v>2</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="D27" s="29">
+      <c r="D27" s="15">
         <f>AVERAGE('Respuestas Encuesta'!F6:F55)</f>
         <v>3.76</v>
       </c>
-      <c r="E27" s="17" t="s">
+      <c r="E27" s="2" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="17">
+      <c r="A28" s="2">
         <v>3</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="15">
         <f>AVERAGE('Respuestas Encuesta'!G6:G55)</f>
         <v>3.46</v>
       </c>
-      <c r="E28" s="17" t="s">
+      <c r="E28" s="2" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="68.400000000000006" x14ac:dyDescent="0.3">
-      <c r="A29" s="17">
+      <c r="A29" s="2">
         <v>4</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D29" s="22" t="s">
+      <c r="D29" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E29" s="17" t="s">
+      <c r="E29" s="2" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="91.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="17">
+      <c r="A30" s="2">
         <v>5</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="D30" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="2" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="46" t="s">
         <v>165</v>
       </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
+      <c r="B31" s="46"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3599,1726 +3603,1726 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="38" t="s">
         <v>167</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="46" t="s">
         <v>168</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
     </row>
     <row r="5" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="I5" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="16">
         <v>46034</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="10">
         <v>9</v>
       </c>
-      <c r="E6" s="26" t="str">
+      <c r="E6" s="12" t="str">
         <f t="shared" ref="E6:E37" si="0">IF(D6&gt;=9,"Promotor",IF(D6&gt;=7,"Pasivo","Detractor"))</f>
         <v>Promotor</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="10">
         <v>5</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="10">
         <v>5</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="I6" s="17" t="s">
+      <c r="I6" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J6" s="17" t="s">
+      <c r="J6" s="2" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="16">
         <v>46033</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="10">
         <v>9</v>
       </c>
-      <c r="E7" s="26" t="str">
+      <c r="E7" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Promotor</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="10">
         <v>4</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="10">
         <v>4</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="I7" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="J7" s="17" t="s">
+      <c r="J7" s="2" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="16">
         <v>46034</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="10">
         <v>8</v>
       </c>
-      <c r="E8" s="27" t="str">
+      <c r="E8" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Pasivo</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="10">
         <v>4</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="10">
         <v>1</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="H8" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="I8" s="17" t="s">
+      <c r="I8" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J8" s="17" t="s">
+      <c r="J8" s="2" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="16">
         <v>46055</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="10">
         <v>8</v>
       </c>
-      <c r="E9" s="27" t="str">
+      <c r="E9" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Pasivo</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="10">
         <v>5</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="10">
         <v>2</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="H9" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="I9" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="J9" s="17" t="s">
+      <c r="J9" s="2" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="16">
         <v>46030</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="10">
         <v>9</v>
       </c>
-      <c r="E10" s="26" t="str">
+      <c r="E10" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Promotor</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="10">
         <v>5</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="10">
         <v>3</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="H10" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="I10" s="17" t="s">
+      <c r="I10" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="J10" s="17" t="s">
+      <c r="J10" s="2" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="16">
         <v>46043</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="10">
         <v>9</v>
       </c>
-      <c r="E11" s="26" t="str">
+      <c r="E11" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Promotor</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="10">
         <v>3</v>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="10">
         <v>4</v>
       </c>
-      <c r="H11" s="17" t="s">
+      <c r="H11" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="I11" s="17" t="s">
+      <c r="I11" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J11" s="17" t="s">
+      <c r="J11" s="2" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="16">
         <v>46071</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="10">
         <v>8</v>
       </c>
-      <c r="E12" s="27" t="str">
+      <c r="E12" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Pasivo</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="10">
         <v>4</v>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="10">
         <v>4</v>
       </c>
-      <c r="H12" s="17" t="s">
+      <c r="H12" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="I12" s="17" t="s">
+      <c r="I12" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J12" s="17" t="s">
+      <c r="J12" s="2" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="16">
         <v>46037</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="10">
         <v>3</v>
       </c>
-      <c r="E13" s="28" t="str">
+      <c r="E13" s="14" t="str">
         <f t="shared" si="0"/>
         <v>Detractor</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="10">
         <v>3</v>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="10">
         <v>2</v>
       </c>
-      <c r="H13" s="17" t="s">
+      <c r="H13" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="I13" s="17" t="s">
+      <c r="I13" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J13" s="17" t="s">
+      <c r="J13" s="2" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="16">
         <v>46030</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="10">
         <v>7</v>
       </c>
-      <c r="E14" s="27" t="str">
+      <c r="E14" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Pasivo</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="10">
         <v>4</v>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="10">
         <v>4</v>
       </c>
-      <c r="H14" s="17" t="s">
+      <c r="H14" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="I14" s="17" t="s">
+      <c r="I14" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="J14" s="17" t="s">
+      <c r="J14" s="2" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="16">
         <v>46069</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="10">
         <v>9</v>
       </c>
-      <c r="E15" s="26" t="str">
+      <c r="E15" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Promotor</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="10">
         <v>5</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="10">
         <v>5</v>
       </c>
-      <c r="H15" s="17" t="s">
+      <c r="H15" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="I15" s="17" t="s">
+      <c r="I15" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="J15" s="17" t="s">
+      <c r="J15" s="2" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="16">
         <v>46027</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="10">
         <v>7</v>
       </c>
-      <c r="E16" s="27" t="str">
+      <c r="E16" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Pasivo</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="10">
         <v>3</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="10">
         <v>3</v>
       </c>
-      <c r="H16" s="17" t="s">
+      <c r="H16" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="I16" s="17" t="s">
+      <c r="I16" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="J16" s="17" t="s">
+      <c r="J16" s="2" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="16">
         <v>46038</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="10">
         <v>7</v>
       </c>
-      <c r="E17" s="27" t="str">
+      <c r="E17" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Pasivo</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="10">
         <v>2</v>
       </c>
-      <c r="G17" s="24">
+      <c r="G17" s="10">
         <v>3</v>
       </c>
-      <c r="H17" s="17" t="s">
+      <c r="H17" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="I17" s="17" t="s">
+      <c r="I17" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="J17" s="17" t="s">
+      <c r="J17" s="2" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="B18" s="30">
+      <c r="B18" s="16">
         <v>46038</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="10">
         <v>10</v>
       </c>
-      <c r="E18" s="26" t="str">
+      <c r="E18" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Promotor</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="10">
         <v>4</v>
       </c>
-      <c r="G18" s="24">
+      <c r="G18" s="10">
         <v>5</v>
       </c>
-      <c r="H18" s="17" t="s">
+      <c r="H18" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="I18" s="17" t="s">
+      <c r="I18" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J18" s="17" t="s">
+      <c r="J18" s="2" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="16">
         <v>46070</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="C19" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="10">
         <v>10</v>
       </c>
-      <c r="E19" s="26" t="str">
+      <c r="E19" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Promotor</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="10">
         <v>4</v>
       </c>
-      <c r="G19" s="24">
+      <c r="G19" s="10">
         <v>2</v>
       </c>
-      <c r="H19" s="17" t="s">
+      <c r="H19" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="I19" s="17" t="s">
+      <c r="I19" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J19" s="17" t="s">
+      <c r="J19" s="2" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="16">
         <v>46037</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="10">
         <v>5</v>
       </c>
-      <c r="E20" s="28" t="str">
+      <c r="E20" s="14" t="str">
         <f t="shared" si="0"/>
         <v>Detractor</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="10">
         <v>3</v>
       </c>
-      <c r="G20" s="24">
+      <c r="G20" s="10">
         <v>2</v>
       </c>
-      <c r="H20" s="17" t="s">
+      <c r="H20" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="I20" s="17" t="s">
+      <c r="I20" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="J20" s="17" t="s">
+      <c r="J20" s="2" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="16">
         <v>46071</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="10">
         <v>6</v>
       </c>
-      <c r="E21" s="28" t="str">
+      <c r="E21" s="14" t="str">
         <f t="shared" si="0"/>
         <v>Detractor</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="10">
         <v>2</v>
       </c>
-      <c r="G21" s="24">
+      <c r="G21" s="10">
         <v>2</v>
       </c>
-      <c r="H21" s="17" t="s">
+      <c r="H21" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="I21" s="17" t="s">
+      <c r="I21" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="J21" s="17" t="s">
+      <c r="J21" s="2" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="B22" s="30">
+      <c r="B22" s="16">
         <v>46056</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="C22" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="10">
         <v>2</v>
       </c>
-      <c r="E22" s="28" t="str">
+      <c r="E22" s="14" t="str">
         <f t="shared" si="0"/>
         <v>Detractor</v>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="10">
         <v>1</v>
       </c>
-      <c r="G22" s="24">
+      <c r="G22" s="10">
         <v>2</v>
       </c>
-      <c r="H22" s="17" t="s">
+      <c r="H22" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="I22" s="17" t="s">
+      <c r="I22" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J22" s="17" t="s">
+      <c r="J22" s="2" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="B23" s="30">
+      <c r="B23" s="16">
         <v>46067</v>
       </c>
-      <c r="C23" s="24" t="s">
+      <c r="C23" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D23" s="24">
+      <c r="D23" s="10">
         <v>10</v>
       </c>
-      <c r="E23" s="26" t="str">
+      <c r="E23" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Promotor</v>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="10">
         <v>4</v>
       </c>
-      <c r="G23" s="24">
+      <c r="G23" s="10">
         <v>3</v>
       </c>
-      <c r="H23" s="17" t="s">
+      <c r="H23" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="I23" s="17" t="s">
+      <c r="I23" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J23" s="17" t="s">
+      <c r="J23" s="2" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="B24" s="30">
+      <c r="B24" s="16">
         <v>46032</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D24" s="24">
+      <c r="D24" s="10">
         <v>6</v>
       </c>
-      <c r="E24" s="28" t="str">
+      <c r="E24" s="14" t="str">
         <f t="shared" si="0"/>
         <v>Detractor</v>
       </c>
-      <c r="F24" s="24">
+      <c r="F24" s="10">
         <v>4</v>
       </c>
-      <c r="G24" s="24">
+      <c r="G24" s="10">
         <v>3</v>
       </c>
-      <c r="H24" s="17" t="s">
+      <c r="H24" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="I24" s="17" t="s">
+      <c r="I24" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J24" s="17" t="s">
+      <c r="J24" s="2" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="24" t="s">
+      <c r="A25" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="B25" s="30">
+      <c r="B25" s="16">
         <v>46029</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="C25" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D25" s="24">
+      <c r="D25" s="10">
         <v>8</v>
       </c>
-      <c r="E25" s="27" t="str">
+      <c r="E25" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Pasivo</v>
       </c>
-      <c r="F25" s="24">
+      <c r="F25" s="10">
         <v>2</v>
       </c>
-      <c r="G25" s="24">
+      <c r="G25" s="10">
         <v>4</v>
       </c>
-      <c r="H25" s="17" t="s">
+      <c r="H25" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="I25" s="17" t="s">
+      <c r="I25" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="J25" s="17" t="s">
+      <c r="J25" s="2" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="24" t="s">
+      <c r="A26" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="B26" s="30">
+      <c r="B26" s="16">
         <v>46072</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D26" s="24">
+      <c r="D26" s="10">
         <v>7</v>
       </c>
-      <c r="E26" s="27" t="str">
+      <c r="E26" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Pasivo</v>
       </c>
-      <c r="F26" s="24">
+      <c r="F26" s="10">
         <v>3</v>
       </c>
-      <c r="G26" s="24">
+      <c r="G26" s="10">
         <v>4</v>
       </c>
-      <c r="H26" s="17" t="s">
+      <c r="H26" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="I26" s="17" t="s">
+      <c r="I26" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J26" s="17" t="s">
+      <c r="J26" s="2" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="24" t="s">
+      <c r="A27" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="B27" s="30">
+      <c r="B27" s="16">
         <v>46032</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="C27" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="10">
         <v>9</v>
       </c>
-      <c r="E27" s="26" t="str">
+      <c r="E27" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Promotor</v>
       </c>
-      <c r="F27" s="24">
+      <c r="F27" s="10">
         <v>4</v>
       </c>
-      <c r="G27" s="24">
+      <c r="G27" s="10">
         <v>3</v>
       </c>
-      <c r="H27" s="17" t="s">
+      <c r="H27" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="I27" s="17" t="s">
+      <c r="I27" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J27" s="17" t="s">
+      <c r="J27" s="2" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="24" t="s">
+      <c r="A28" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="B28" s="30">
+      <c r="B28" s="16">
         <v>46069</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D28" s="24">
+      <c r="D28" s="10">
         <v>3</v>
       </c>
-      <c r="E28" s="28" t="str">
+      <c r="E28" s="14" t="str">
         <f t="shared" si="0"/>
         <v>Detractor</v>
       </c>
-      <c r="F28" s="24">
+      <c r="F28" s="10">
         <v>1</v>
       </c>
-      <c r="G28" s="24">
+      <c r="G28" s="10">
         <v>1</v>
       </c>
-      <c r="H28" s="17" t="s">
+      <c r="H28" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="I28" s="17" t="s">
+      <c r="I28" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="J28" s="17" t="s">
+      <c r="J28" s="2" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="24" t="s">
+      <c r="A29" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="B29" s="30">
+      <c r="B29" s="16">
         <v>46046</v>
       </c>
-      <c r="C29" s="24" t="s">
+      <c r="C29" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D29" s="24">
+      <c r="D29" s="10">
         <v>9</v>
       </c>
-      <c r="E29" s="26" t="str">
+      <c r="E29" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Promotor</v>
       </c>
-      <c r="F29" s="24">
+      <c r="F29" s="10">
         <v>4</v>
       </c>
-      <c r="G29" s="24">
+      <c r="G29" s="10">
         <v>4</v>
       </c>
-      <c r="H29" s="17" t="s">
+      <c r="H29" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="I29" s="17" t="s">
+      <c r="I29" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="J29" s="17" t="s">
+      <c r="J29" s="2" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="24" t="s">
+      <c r="A30" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="B30" s="30">
+      <c r="B30" s="16">
         <v>46047</v>
       </c>
-      <c r="C30" s="24" t="s">
+      <c r="C30" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D30" s="24">
+      <c r="D30" s="10">
         <v>10</v>
       </c>
-      <c r="E30" s="26" t="str">
+      <c r="E30" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Promotor</v>
       </c>
-      <c r="F30" s="24">
+      <c r="F30" s="10">
         <v>4</v>
       </c>
-      <c r="G30" s="24">
+      <c r="G30" s="10">
         <v>5</v>
       </c>
-      <c r="H30" s="17" t="s">
+      <c r="H30" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="I30" s="17" t="s">
+      <c r="I30" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="J30" s="17" t="s">
+      <c r="J30" s="2" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="24" t="s">
+      <c r="A31" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="B31" s="30">
+      <c r="B31" s="16">
         <v>46050</v>
       </c>
-      <c r="C31" s="24" t="s">
+      <c r="C31" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="24">
+      <c r="D31" s="10">
         <v>10</v>
       </c>
-      <c r="E31" s="26" t="str">
+      <c r="E31" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Promotor</v>
       </c>
-      <c r="F31" s="24">
+      <c r="F31" s="10">
         <v>5</v>
       </c>
-      <c r="G31" s="24">
+      <c r="G31" s="10">
         <v>4</v>
       </c>
-      <c r="H31" s="17" t="s">
+      <c r="H31" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="I31" s="17" t="s">
+      <c r="I31" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J31" s="17" t="s">
+      <c r="J31" s="2" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="24" t="s">
+      <c r="A32" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="B32" s="30">
+      <c r="B32" s="16">
         <v>46058</v>
       </c>
-      <c r="C32" s="24" t="s">
+      <c r="C32" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D32" s="24">
+      <c r="D32" s="10">
         <v>7</v>
       </c>
-      <c r="E32" s="27" t="str">
+      <c r="E32" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Pasivo</v>
       </c>
-      <c r="F32" s="24">
+      <c r="F32" s="10">
         <v>4</v>
       </c>
-      <c r="G32" s="24">
+      <c r="G32" s="10">
         <v>3</v>
       </c>
-      <c r="H32" s="17" t="s">
+      <c r="H32" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="I32" s="17" t="s">
+      <c r="I32" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="J32" s="17" t="s">
+      <c r="J32" s="2" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="24" t="s">
+      <c r="A33" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B33" s="30">
+      <c r="B33" s="16">
         <v>46027</v>
       </c>
-      <c r="C33" s="24" t="s">
+      <c r="C33" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D33" s="24">
+      <c r="D33" s="10">
         <v>10</v>
       </c>
-      <c r="E33" s="26" t="str">
+      <c r="E33" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Promotor</v>
       </c>
-      <c r="F33" s="24">
+      <c r="F33" s="10">
         <v>3</v>
       </c>
-      <c r="G33" s="24">
+      <c r="G33" s="10">
         <v>5</v>
       </c>
-      <c r="H33" s="17" t="s">
+      <c r="H33" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="I33" s="17" t="s">
+      <c r="I33" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="J33" s="17" t="s">
+      <c r="J33" s="2" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="24" t="s">
+      <c r="A34" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="B34" s="30">
+      <c r="B34" s="16">
         <v>46072</v>
       </c>
-      <c r="C34" s="24" t="s">
+      <c r="C34" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D34" s="24">
+      <c r="D34" s="10">
         <v>10</v>
       </c>
-      <c r="E34" s="26" t="str">
+      <c r="E34" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Promotor</v>
       </c>
-      <c r="F34" s="24">
+      <c r="F34" s="10">
         <v>4</v>
       </c>
-      <c r="G34" s="24">
+      <c r="G34" s="10">
         <v>4</v>
       </c>
-      <c r="H34" s="17" t="s">
+      <c r="H34" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="I34" s="17" t="s">
+      <c r="I34" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J34" s="17" t="s">
+      <c r="J34" s="2" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="24" t="s">
+      <c r="A35" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="B35" s="30">
+      <c r="B35" s="16">
         <v>46031</v>
       </c>
-      <c r="C35" s="24" t="s">
+      <c r="C35" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D35" s="24">
+      <c r="D35" s="10">
         <v>7</v>
       </c>
-      <c r="E35" s="27" t="str">
+      <c r="E35" s="13" t="str">
         <f t="shared" si="0"/>
         <v>Pasivo</v>
       </c>
-      <c r="F35" s="24">
+      <c r="F35" s="10">
         <v>2</v>
       </c>
-      <c r="G35" s="24">
+      <c r="G35" s="10">
         <v>4</v>
       </c>
-      <c r="H35" s="17" t="s">
+      <c r="H35" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="I35" s="17" t="s">
+      <c r="I35" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="J35" s="17" t="s">
+      <c r="J35" s="2" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="24" t="s">
+      <c r="A36" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="B36" s="30">
+      <c r="B36" s="16">
         <v>46040</v>
       </c>
-      <c r="C36" s="24" t="s">
+      <c r="C36" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D36" s="24">
+      <c r="D36" s="10">
         <v>10</v>
       </c>
-      <c r="E36" s="26" t="str">
+      <c r="E36" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Promotor</v>
       </c>
-      <c r="F36" s="24">
+      <c r="F36" s="10">
         <v>4</v>
       </c>
-      <c r="G36" s="24">
+      <c r="G36" s="10">
         <v>3</v>
       </c>
-      <c r="H36" s="17" t="s">
+      <c r="H36" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="I36" s="17" t="s">
+      <c r="I36" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J36" s="17" t="s">
+      <c r="J36" s="2" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="24" t="s">
+      <c r="A37" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="16">
         <v>46048</v>
       </c>
-      <c r="C37" s="24" t="s">
+      <c r="C37" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D37" s="24">
+      <c r="D37" s="10">
         <v>10</v>
       </c>
-      <c r="E37" s="26" t="str">
+      <c r="E37" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Promotor</v>
       </c>
-      <c r="F37" s="24">
+      <c r="F37" s="10">
         <v>4</v>
       </c>
-      <c r="G37" s="24">
+      <c r="G37" s="10">
         <v>5</v>
       </c>
-      <c r="H37" s="17" t="s">
+      <c r="H37" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="I37" s="17" t="s">
+      <c r="I37" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J37" s="17" t="s">
+      <c r="J37" s="2" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="24" t="s">
+      <c r="A38" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="B38" s="30">
+      <c r="B38" s="16">
         <v>46046</v>
       </c>
-      <c r="C38" s="24" t="s">
+      <c r="C38" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D38" s="24">
+      <c r="D38" s="10">
         <v>0</v>
       </c>
-      <c r="E38" s="28" t="str">
-        <f t="shared" ref="E38:E69" si="1">IF(D38&gt;=9,"Promotor",IF(D38&gt;=7,"Pasivo","Detractor"))</f>
+      <c r="E38" s="14" t="str">
+        <f t="shared" ref="E38:E55" si="1">IF(D38&gt;=9,"Promotor",IF(D38&gt;=7,"Pasivo","Detractor"))</f>
         <v>Detractor</v>
       </c>
-      <c r="F38" s="24">
+      <c r="F38" s="10">
         <v>2</v>
       </c>
-      <c r="G38" s="24">
+      <c r="G38" s="10">
         <v>3</v>
       </c>
-      <c r="H38" s="17" t="s">
+      <c r="H38" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="I38" s="17" t="s">
+      <c r="I38" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="J38" s="17" t="s">
+      <c r="J38" s="2" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="24" t="s">
+      <c r="A39" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="B39" s="30">
+      <c r="B39" s="16">
         <v>46059</v>
       </c>
-      <c r="C39" s="24" t="s">
+      <c r="C39" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D39" s="24">
+      <c r="D39" s="10">
         <v>9</v>
       </c>
-      <c r="E39" s="26" t="str">
+      <c r="E39" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Promotor</v>
       </c>
-      <c r="F39" s="24">
+      <c r="F39" s="10">
         <v>5</v>
       </c>
-      <c r="G39" s="24">
+      <c r="G39" s="10">
         <v>5</v>
       </c>
-      <c r="H39" s="17" t="s">
+      <c r="H39" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="I39" s="17" t="s">
+      <c r="I39" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="J39" s="17" t="s">
+      <c r="J39" s="2" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="24" t="s">
+      <c r="A40" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="B40" s="30">
+      <c r="B40" s="16">
         <v>46070</v>
       </c>
-      <c r="C40" s="24" t="s">
+      <c r="C40" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D40" s="24">
+      <c r="D40" s="10">
         <v>10</v>
       </c>
-      <c r="E40" s="26" t="str">
+      <c r="E40" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Promotor</v>
       </c>
-      <c r="F40" s="24">
+      <c r="F40" s="10">
         <v>4</v>
       </c>
-      <c r="G40" s="24">
+      <c r="G40" s="10">
         <v>1</v>
       </c>
-      <c r="H40" s="17" t="s">
+      <c r="H40" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="I40" s="17" t="s">
+      <c r="I40" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J40" s="17" t="s">
+      <c r="J40" s="2" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="24" t="s">
+      <c r="A41" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="B41" s="30">
+      <c r="B41" s="16">
         <v>46065</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D41" s="24">
+      <c r="D41" s="10">
         <v>9</v>
       </c>
-      <c r="E41" s="26" t="str">
+      <c r="E41" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Promotor</v>
       </c>
-      <c r="F41" s="24">
+      <c r="F41" s="10">
         <v>5</v>
       </c>
-      <c r="G41" s="24">
+      <c r="G41" s="10">
         <v>4</v>
       </c>
-      <c r="H41" s="17" t="s">
+      <c r="H41" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="I41" s="17" t="s">
+      <c r="I41" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J41" s="17" t="s">
+      <c r="J41" s="2" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="24" t="s">
+      <c r="A42" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="B42" s="30">
+      <c r="B42" s="16">
         <v>46068</v>
       </c>
-      <c r="C42" s="24" t="s">
+      <c r="C42" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D42" s="24">
+      <c r="D42" s="10">
         <v>9</v>
       </c>
-      <c r="E42" s="26" t="str">
+      <c r="E42" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Promotor</v>
       </c>
-      <c r="F42" s="24">
+      <c r="F42" s="10">
         <v>5</v>
       </c>
-      <c r="G42" s="24">
+      <c r="G42" s="10">
         <v>4</v>
       </c>
-      <c r="H42" s="17" t="s">
+      <c r="H42" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="I42" s="17" t="s">
+      <c r="I42" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J42" s="17" t="s">
+      <c r="J42" s="2" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="24" t="s">
+      <c r="A43" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="B43" s="30">
+      <c r="B43" s="16">
         <v>46040</v>
       </c>
-      <c r="C43" s="24" t="s">
+      <c r="C43" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D43" s="24">
+      <c r="D43" s="10">
         <v>9</v>
       </c>
-      <c r="E43" s="26" t="str">
+      <c r="E43" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Promotor</v>
       </c>
-      <c r="F43" s="24">
+      <c r="F43" s="10">
         <v>5</v>
       </c>
-      <c r="G43" s="24">
+      <c r="G43" s="10">
         <v>5</v>
       </c>
-      <c r="H43" s="17" t="s">
+      <c r="H43" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="I43" s="17" t="s">
+      <c r="I43" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J43" s="17" t="s">
+      <c r="J43" s="2" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="24" t="s">
+      <c r="A44" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="B44" s="30">
+      <c r="B44" s="16">
         <v>46059</v>
       </c>
-      <c r="C44" s="24" t="s">
+      <c r="C44" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D44" s="24">
+      <c r="D44" s="10">
         <v>9</v>
       </c>
-      <c r="E44" s="26" t="str">
+      <c r="E44" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Promotor</v>
       </c>
-      <c r="F44" s="24">
+      <c r="F44" s="10">
         <v>5</v>
       </c>
-      <c r="G44" s="24">
+      <c r="G44" s="10">
         <v>3</v>
       </c>
-      <c r="H44" s="17" t="s">
+      <c r="H44" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="I44" s="17" t="s">
+      <c r="I44" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="J44" s="17" t="s">
+      <c r="J44" s="2" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="24" t="s">
+      <c r="A45" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="B45" s="30">
+      <c r="B45" s="16">
         <v>46035</v>
       </c>
-      <c r="C45" s="24" t="s">
+      <c r="C45" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D45" s="24">
+      <c r="D45" s="10">
         <v>9</v>
       </c>
-      <c r="E45" s="26" t="str">
+      <c r="E45" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Promotor</v>
       </c>
-      <c r="F45" s="24">
+      <c r="F45" s="10">
         <v>5</v>
       </c>
-      <c r="G45" s="24">
+      <c r="G45" s="10">
         <v>3</v>
       </c>
-      <c r="H45" s="17" t="s">
+      <c r="H45" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="I45" s="17" t="s">
+      <c r="I45" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="J45" s="17" t="s">
+      <c r="J45" s="2" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="24" t="s">
+      <c r="A46" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="B46" s="30">
+      <c r="B46" s="16">
         <v>46042</v>
       </c>
-      <c r="C46" s="24" t="s">
+      <c r="C46" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D46" s="24">
+      <c r="D46" s="10">
         <v>10</v>
       </c>
-      <c r="E46" s="26" t="str">
+      <c r="E46" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Promotor</v>
       </c>
-      <c r="F46" s="24">
+      <c r="F46" s="10">
         <v>5</v>
       </c>
-      <c r="G46" s="24">
+      <c r="G46" s="10">
         <v>4</v>
       </c>
-      <c r="H46" s="17" t="s">
+      <c r="H46" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="I46" s="17" t="s">
+      <c r="I46" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J46" s="17" t="s">
+      <c r="J46" s="2" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="24" t="s">
+      <c r="A47" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="B47" s="30">
+      <c r="B47" s="16">
         <v>46063</v>
       </c>
-      <c r="C47" s="24" t="s">
+      <c r="C47" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D47" s="24">
+      <c r="D47" s="10">
         <v>8</v>
       </c>
-      <c r="E47" s="27" t="str">
+      <c r="E47" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Pasivo</v>
       </c>
-      <c r="F47" s="24">
+      <c r="F47" s="10">
         <v>4</v>
       </c>
-      <c r="G47" s="24">
+      <c r="G47" s="10">
         <v>2</v>
       </c>
-      <c r="H47" s="17" t="s">
+      <c r="H47" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="I47" s="17" t="s">
+      <c r="I47" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="J47" s="17" t="s">
+      <c r="J47" s="2" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="24" t="s">
+      <c r="A48" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="B48" s="30">
+      <c r="B48" s="16">
         <v>46037</v>
       </c>
-      <c r="C48" s="24" t="s">
+      <c r="C48" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D48" s="24">
+      <c r="D48" s="10">
         <v>9</v>
       </c>
-      <c r="E48" s="26" t="str">
+      <c r="E48" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Promotor</v>
       </c>
-      <c r="F48" s="24">
+      <c r="F48" s="10">
         <v>4</v>
       </c>
-      <c r="G48" s="24">
+      <c r="G48" s="10">
         <v>3</v>
       </c>
-      <c r="H48" s="17" t="s">
+      <c r="H48" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="I48" s="17" t="s">
+      <c r="I48" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="J48" s="17" t="s">
+      <c r="J48" s="2" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="24" t="s">
+      <c r="A49" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="B49" s="30">
+      <c r="B49" s="16">
         <v>46057</v>
       </c>
-      <c r="C49" s="24" t="s">
+      <c r="C49" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D49" s="24">
+      <c r="D49" s="10">
         <v>10</v>
       </c>
-      <c r="E49" s="26" t="str">
+      <c r="E49" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Promotor</v>
       </c>
-      <c r="F49" s="24">
+      <c r="F49" s="10">
         <v>4</v>
       </c>
-      <c r="G49" s="24">
+      <c r="G49" s="10">
         <v>4</v>
       </c>
-      <c r="H49" s="17" t="s">
+      <c r="H49" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="I49" s="17" t="s">
+      <c r="I49" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="J49" s="17" t="s">
+      <c r="J49" s="2" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="24" t="s">
+      <c r="A50" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="B50" s="30">
+      <c r="B50" s="16">
         <v>46028</v>
       </c>
-      <c r="C50" s="24" t="s">
+      <c r="C50" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D50" s="24">
+      <c r="D50" s="10">
         <v>10</v>
       </c>
-      <c r="E50" s="26" t="str">
+      <c r="E50" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Promotor</v>
       </c>
-      <c r="F50" s="24">
+      <c r="F50" s="10">
         <v>4</v>
       </c>
-      <c r="G50" s="24">
+      <c r="G50" s="10">
         <v>5</v>
       </c>
-      <c r="H50" s="17" t="s">
+      <c r="H50" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="I50" s="17" t="s">
+      <c r="I50" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J50" s="17" t="s">
+      <c r="J50" s="2" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="24" t="s">
+      <c r="A51" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="B51" s="30">
+      <c r="B51" s="16">
         <v>46052</v>
       </c>
-      <c r="C51" s="24" t="s">
+      <c r="C51" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D51" s="24">
+      <c r="D51" s="10">
         <v>7</v>
       </c>
-      <c r="E51" s="27" t="str">
+      <c r="E51" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Pasivo</v>
       </c>
-      <c r="F51" s="24">
+      <c r="F51" s="10">
         <v>3</v>
       </c>
-      <c r="G51" s="24">
+      <c r="G51" s="10">
         <v>4</v>
       </c>
-      <c r="H51" s="17" t="s">
+      <c r="H51" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="I51" s="17" t="s">
+      <c r="I51" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="J51" s="17" t="s">
+      <c r="J51" s="2" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="24" t="s">
+      <c r="A52" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="B52" s="30">
+      <c r="B52" s="16">
         <v>46063</v>
       </c>
-      <c r="C52" s="24" t="s">
+      <c r="C52" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D52" s="24">
+      <c r="D52" s="10">
         <v>10</v>
       </c>
-      <c r="E52" s="26" t="str">
+      <c r="E52" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Promotor</v>
       </c>
-      <c r="F52" s="24">
+      <c r="F52" s="10">
         <v>5</v>
       </c>
-      <c r="G52" s="24">
+      <c r="G52" s="10">
         <v>5</v>
       </c>
-      <c r="H52" s="17" t="s">
+      <c r="H52" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="I52" s="17" t="s">
+      <c r="I52" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J52" s="17" t="s">
+      <c r="J52" s="2" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="24" t="s">
+      <c r="A53" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="B53" s="30">
+      <c r="B53" s="16">
         <v>46062</v>
       </c>
-      <c r="C53" s="24" t="s">
+      <c r="C53" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D53" s="24">
+      <c r="D53" s="10">
         <v>9</v>
       </c>
-      <c r="E53" s="26" t="str">
+      <c r="E53" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Promotor</v>
       </c>
-      <c r="F53" s="24">
+      <c r="F53" s="10">
         <v>4</v>
       </c>
-      <c r="G53" s="24">
+      <c r="G53" s="10">
         <v>3</v>
       </c>
-      <c r="H53" s="17" t="s">
+      <c r="H53" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="I53" s="17" t="s">
+      <c r="I53" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="J53" s="17" t="s">
+      <c r="J53" s="2" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="24" t="s">
+      <c r="A54" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="B54" s="30">
+      <c r="B54" s="16">
         <v>46044</v>
       </c>
-      <c r="C54" s="24" t="s">
+      <c r="C54" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D54" s="24">
+      <c r="D54" s="10">
         <v>10</v>
       </c>
-      <c r="E54" s="26" t="str">
+      <c r="E54" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Promotor</v>
       </c>
-      <c r="F54" s="24">
+      <c r="F54" s="10">
         <v>4</v>
       </c>
-      <c r="G54" s="24">
+      <c r="G54" s="10">
         <v>5</v>
       </c>
-      <c r="H54" s="17" t="s">
+      <c r="H54" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="I54" s="17" t="s">
+      <c r="I54" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J54" s="17" t="s">
+      <c r="J54" s="2" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="24" t="s">
+      <c r="A55" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="B55" s="30">
+      <c r="B55" s="16">
         <v>46065</v>
       </c>
-      <c r="C55" s="24" t="s">
+      <c r="C55" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D55" s="24">
+      <c r="D55" s="10">
         <v>4</v>
       </c>
-      <c r="E55" s="28" t="str">
+      <c r="E55" s="14" t="str">
         <f t="shared" si="1"/>
         <v>Detractor</v>
       </c>
-      <c r="F55" s="24">
+      <c r="F55" s="10">
         <v>2</v>
       </c>
-      <c r="G55" s="24">
+      <c r="G55" s="10">
         <v>2</v>
       </c>
-      <c r="H55" s="17" t="s">
+      <c r="H55" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="I55" s="17" t="s">
+      <c r="I55" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="J55" s="17" t="s">
+      <c r="J55" s="2" t="s">
         <v>225</v>
       </c>
     </row>
@@ -5347,469 +5351,469 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="37" t="s">
         <v>251</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="38" t="s">
         <v>252</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="46" t="s">
         <v>253</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
     </row>
     <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="4" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="1" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="17">
         <f>COUNTA('Reseñas y Encuesta'!H5:H17)</f>
         <v>13</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="2" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="18">
         <f>AVERAGE('Reseñas y Encuesta'!D5:D17)</f>
         <v>3.5454545454545454</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="D8" s="17" t="str">
+      <c r="D8" s="2" t="str">
         <f>IF(B8&gt;=4.5,"Excelente: la percepción general es muy positiva.",IF(B8&gt;=4,"Muy buena, aunque con margen de mejora.",IF(B8&gt;=3,"Regular: hay señales de insatisfacción relevantes.","Crítica: predominan las experiencias negativas."))) &amp; "  Resultado actual: " &amp; TEXT(B8,"0.0") &amp; "/5."</f>
         <v>Regular: hay señales de insatisfacción relevantes.  Resultado actual: 3.5/5.</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="19">
         <f>COUNTIF('Reseñas y Encuesta'!H5:H17,"Positivo")/COUNTA('Reseñas y Encuesta'!H5:H17)</f>
         <v>0.38461538461538464</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="D9" s="17" t="str">
+      <c r="D9" s="2" t="str">
         <f>IF(B9&gt;=0.6,"Alta: predominan las experiencias positivas.",IF(B9&gt;=0.4,"Moderada.","Baja: conviene reforzar la comunicación de los puntos fuertes.")) &amp; "  Resultado actual: " &amp; TEXT(B9,"0%")</f>
         <v>Baja: conviene reforzar la comunicación de los puntos fuertes.  Resultado actual: 38%</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="19">
         <f>COUNTIF('Reseñas y Encuesta'!H5:H17,"Negativo")/COUNTA('Reseñas y Encuesta'!H5:H17)</f>
         <v>0.30769230769230771</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="D10" s="17" t="str">
+      <c r="D10" s="2" t="str">
         <f>IF(B10&gt;=0.5,"Alta: más de la mitad de la muestra es negativa (recordar que son reseñas construidas para ilustrar cada hallazgo, no una muestra real).",IF(B10&gt;=0.25,"Moderada: hay puntos de fricción a atender.","Baja.")) &amp; "  Resultado actual: " &amp; TEXT(B10,"0%")</f>
         <v>Moderada: hay puntos de fricción a atender.  Resultado actual: 31%</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="B11" s="33">
+      <c r="B11" s="19">
         <f>COUNTIF('Reseñas y Encuesta'!H5:H17,"Mixto")/COUNTA('Reseñas y Encuesta'!H5:H17)</f>
         <v>0.30769230769230771</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D11" s="17" t="str">
+      <c r="D11" s="2" t="str">
         <f>IF(B11&gt;=0.2,"Relevante: conviene revisar qué puntos de contacto generan esa ambivalencia.","Poco relevante.") &amp; "  Resultado actual: " &amp; TEXT(B11,"0%")</f>
         <v>Relevante: conviene revisar qué puntos de contacto generan esa ambivalencia.  Resultado actual: 31%</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="5" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="1" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="10">
         <f>COUNTIF('Reseñas y Encuesta'!G5:G17,A15)</f>
         <v>5</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="10">
         <f>COUNTIF('Respuestas Encuesta'!I6:I55,A15)</f>
         <v>19</v>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="17">
         <f>B15+C15</f>
         <v>24</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="20">
         <f>D15/63</f>
         <v>0.38095238095238093</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="F15" s="3" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="10">
         <f>COUNTIF('Reseñas y Encuesta'!G5:G17,A16)</f>
         <v>2</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="10">
         <f>COUNTIF('Respuestas Encuesta'!I6:I55,A16)</f>
         <v>5</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="17">
         <f>B16+C16</f>
         <v>7</v>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="20">
         <f>D16/63</f>
         <v>0.1111111111111111</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="3" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B17" s="24">
+      <c r="B17" s="10">
         <f>COUNTIF('Reseñas y Encuesta'!G5:G17,A17)</f>
         <v>2</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="10">
         <f>COUNTIF('Respuestas Encuesta'!I6:I55,A17)</f>
         <v>2</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="17">
         <f>B17+C17</f>
         <v>4</v>
       </c>
-      <c r="E17" s="34">
+      <c r="E17" s="20">
         <f>D17/63</f>
         <v>6.3492063492063489E-2</v>
       </c>
-      <c r="F17" s="22" t="s">
+      <c r="F17" s="3" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B18" s="24">
+      <c r="B18" s="10">
         <f>COUNTIF('Reseñas y Encuesta'!G5:G17,A18)</f>
         <v>2</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="10">
         <f>COUNTIF('Respuestas Encuesta'!I6:I55,A18)</f>
         <v>3</v>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="17">
         <f>B18+C18</f>
         <v>5</v>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="20">
         <f>D18/63</f>
         <v>7.9365079365079361E-2</v>
       </c>
-      <c r="F18" s="22" t="s">
+      <c r="F18" s="3" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B19" s="24">
+      <c r="B19" s="10">
         <f>COUNTIF('Reseñas y Encuesta'!G5:G17,A19)</f>
         <v>2</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="10">
         <f>COUNTIF('Respuestas Encuesta'!I6:I55,A19)</f>
         <v>8</v>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="17">
         <f>B19+C19</f>
         <v>10</v>
       </c>
-      <c r="E19" s="34">
+      <c r="E19" s="20">
         <f>D19/63</f>
         <v>0.15873015873015872</v>
       </c>
-      <c r="F19" s="22" t="s">
+      <c r="F19" s="3" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="4" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
     </row>
     <row r="25" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="1" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="B26" s="24">
+      <c r="B26" s="10">
         <f>COUNTIF('Respuestas Encuesta'!E6:E55,"Promotor")</f>
         <v>30</v>
       </c>
-      <c r="C26" s="34">
+      <c r="C26" s="20">
         <f>IFERROR(B26/SUM($B$26:$B$28),0)</f>
         <v>0.6</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="D26" s="3" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="B27" s="24">
+      <c r="B27" s="10">
         <f>COUNTIF('Respuestas Encuesta'!E6:E55,"Pasivo")</f>
         <v>12</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="20">
         <f>IFERROR(B27/SUM($B$26:$B$28),0)</f>
         <v>0.24</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="D27" s="3" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B28" s="24">
+      <c r="B28" s="10">
         <f>COUNTIF('Respuestas Encuesta'!E6:E55,"Detractor")</f>
         <v>8</v>
       </c>
-      <c r="C28" s="34">
+      <c r="C28" s="20">
         <f>IFERROR(B28/SUM($B$26:$B$28),0)</f>
         <v>0.16</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="D28" s="3" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="35" t="s">
+      <c r="A29" s="21" t="s">
         <v>294</v>
       </c>
-      <c r="B29" s="31">
+      <c r="B29" s="17">
         <f>SUM(B26:B28)</f>
         <v>50</v>
       </c>
-      <c r="C29" s="36"/>
-      <c r="D29" s="4" t="s">
+      <c r="C29" s="22"/>
+      <c r="D29" s="48" t="s">
         <v>295</v>
       </c>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
+      <c r="E29" s="48"/>
+      <c r="F29" s="48"/>
     </row>
     <row r="31" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="35" t="s">
+      <c r="A31" s="21" t="s">
         <v>296</v>
       </c>
-      <c r="B31" s="37">
+      <c r="B31" s="23">
         <f>IF(B29=0,"Cargar datos",(B26-B28)/B29)</f>
         <v>0.44</v>
       </c>
-      <c r="C31" s="3" t="str">
+      <c r="C31" s="47" t="str">
         <f>IF(ISNUMBER(B31),IF(B31&gt;=0.7,"Excelente (nivel de clase mundial).",IF(B31&gt;=0.3,"Muy bueno.",IF(B31&gt;=0,"Aceptable, con oportunidades de mejora.","Crítico: predominan los detractores."))) &amp; "  Resultado actual: " &amp; TEXT(B31,"0%") &amp; "  |  Escala de referencia: menor a 0% necesita mejorar · 0%-30% bueno · 30%-70% muy bueno · mayor a 70% excelente.","Cargar los datos de la encuesta para calcular el NPS.")</f>
         <v>Muy bueno.  Resultado actual: 44%  |  Escala de referencia: menor a 0% necesita mejorar · 0%-30% bueno · 30%-70% muy bueno · mayor a 70% excelente.</v>
       </c>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="47"/>
     </row>
     <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="4" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
     </row>
     <row r="36" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="1" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="24">
+      <c r="A37" s="10">
         <v>5</v>
       </c>
-      <c r="B37" s="24">
+      <c r="B37" s="10">
         <f>COUNTIF('Respuestas Encuesta'!F6:F55,A37)</f>
         <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="24">
+      <c r="A38" s="10">
         <v>4</v>
       </c>
-      <c r="B38" s="24">
+      <c r="B38" s="10">
         <f>COUNTIF('Respuestas Encuesta'!F6:F55,A38)</f>
         <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="24">
+      <c r="A39" s="10">
         <v>3</v>
       </c>
-      <c r="B39" s="24">
+      <c r="B39" s="10">
         <f>COUNTIF('Respuestas Encuesta'!F6:F55,A39)</f>
         <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="24">
+      <c r="A40" s="10">
         <v>2</v>
       </c>
-      <c r="B40" s="24">
+      <c r="B40" s="10">
         <f>COUNTIF('Respuestas Encuesta'!F6:F55,A40)</f>
         <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="24">
+      <c r="A41" s="10">
         <v>1</v>
       </c>
-      <c r="B41" s="24">
+      <c r="B41" s="10">
         <f>COUNTIF('Respuestas Encuesta'!F6:F55,A41)</f>
         <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="35" t="s">
+      <c r="A42" s="21" t="s">
         <v>300</v>
       </c>
-      <c r="B42" s="37">
+      <c r="B42" s="23">
         <f>IF(SUM(B37:B41)=0,"Cargar datos",(B37+B38)/SUM(B37:B41))</f>
         <v>0.7</v>
       </c>
-      <c r="C42" s="3" t="str">
+      <c r="C42" s="47" t="str">
         <f>IF(ISNUMBER(B42),IF(B42&gt;=0.8,"Alto: en línea o por encima del benchmark habitual de 80% en hotelería.",IF(B42&gt;=0.6,"Aceptable, aunque por debajo del benchmark habitual de 80%.","Bajo: conviene priorizar acciones correctivas.")) &amp; "  Resultado actual: " &amp; TEXT(B42,"0%"),"Cargar los datos de la encuesta para calcular el CSAT.")</f>
         <v>Aceptable, aunque por debajo del benchmark habitual de 80%.  Resultado actual: 70%</v>
       </c>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
+      <c r="D42" s="47"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -5837,337 +5841,332 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="37" t="s">
         <v>301</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="38" t="s">
         <v>302</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="24" t="s">
         <v>303</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="50" t="s">
         <v>304</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="50"/>
+      <c r="D4" s="51" t="s">
         <v>305</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="51" t="s">
+      <c r="E4" s="51"/>
+      <c r="F4" s="52" t="s">
         <v>306</v>
       </c>
-      <c r="G4" s="51"/>
-      <c r="H4" s="52" t="s">
+      <c r="G4" s="52"/>
+      <c r="H4" s="53" t="s">
         <v>307</v>
       </c>
-      <c r="I4" s="52"/>
-      <c r="J4" s="53" t="s">
+      <c r="I4" s="53"/>
+      <c r="J4" s="54" t="s">
         <v>308</v>
       </c>
-      <c r="K4" s="53"/>
+      <c r="K4" s="54"/>
     </row>
     <row r="5" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="24" t="s">
         <v>309</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="25" t="s">
         <v>310</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="25" t="s">
         <v>311</v>
       </c>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="26" t="s">
         <v>312</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="F5" s="41" t="s">
+      <c r="F5" s="27" t="s">
         <v>314</v>
       </c>
-      <c r="G5" s="41" t="s">
+      <c r="G5" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="H5" s="42" t="s">
+      <c r="H5" s="28" t="s">
         <v>316</v>
       </c>
-      <c r="I5" s="42" t="s">
+      <c r="I5" s="28" t="s">
         <v>317</v>
       </c>
-      <c r="J5" s="43" t="s">
+      <c r="J5" s="29" t="s">
         <v>318</v>
       </c>
-      <c r="K5" s="43" t="s">
+      <c r="K5" s="29" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="30" t="s">
         <v>320</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="49" t="s">
         <v>321</v>
       </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54" t="s">
+      <c r="C6" s="49"/>
+      <c r="D6" s="49" t="s">
         <v>322</v>
       </c>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54" t="s">
+      <c r="E6" s="49"/>
+      <c r="F6" s="49" t="s">
         <v>323</v>
       </c>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54" t="s">
+      <c r="G6" s="49"/>
+      <c r="H6" s="49" t="s">
         <v>324</v>
       </c>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54" t="s">
+      <c r="I6" s="49"/>
+      <c r="J6" s="49" t="s">
         <v>325</v>
       </c>
-      <c r="K6" s="54"/>
+      <c r="K6" s="49"/>
     </row>
     <row r="7" spans="1:11" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="30" t="s">
         <v>326</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="I7" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="J7" s="17" t="s">
+      <c r="J7" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="K7" s="17" t="s">
+      <c r="K7" s="2" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="30" t="s">
         <v>337</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="H8" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="I8" s="17" t="s">
+      <c r="I8" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="J8" s="17" t="s">
+      <c r="J8" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="K8" s="17" t="s">
+      <c r="K8" s="2" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="30" t="s">
         <v>348</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="G9" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="H9" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="I9" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="J9" s="17" t="s">
+      <c r="J9" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="K9" s="17" t="s">
+      <c r="K9" s="2" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="30" t="s">
         <v>359</v>
       </c>
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="31" t="s">
         <v>360</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="31" t="s">
         <v>361</v>
       </c>
-      <c r="D10" s="45" t="s">
+      <c r="D10" s="31" t="s">
         <v>362</v>
       </c>
-      <c r="E10" s="45" t="s">
+      <c r="E10" s="31" t="s">
         <v>363</v>
       </c>
-      <c r="F10" s="45" t="s">
+      <c r="F10" s="31" t="s">
         <v>364</v>
       </c>
-      <c r="G10" s="45" t="s">
+      <c r="G10" s="31" t="s">
         <v>365</v>
       </c>
-      <c r="H10" s="45" t="s">
+      <c r="H10" s="31" t="s">
         <v>366</v>
       </c>
-      <c r="I10" s="45" t="s">
+      <c r="I10" s="31" t="s">
         <v>367</v>
       </c>
-      <c r="J10" s="45" t="s">
+      <c r="J10" s="31" t="s">
         <v>368</v>
       </c>
-      <c r="K10" s="45" t="s">
+      <c r="K10" s="31" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="30" t="s">
         <v>370</v>
       </c>
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="32" t="s">
         <v>371</v>
       </c>
-      <c r="C11" s="46" t="s">
+      <c r="C11" s="32" t="s">
         <v>372</v>
       </c>
-      <c r="D11" s="46" t="s">
+      <c r="D11" s="32" t="s">
         <v>373</v>
       </c>
-      <c r="E11" s="46" t="s">
+      <c r="E11" s="32" t="s">
         <v>374</v>
       </c>
-      <c r="F11" s="46" t="s">
+      <c r="F11" s="32" t="s">
         <v>375</v>
       </c>
-      <c r="G11" s="46" t="s">
+      <c r="G11" s="32" t="s">
         <v>376</v>
       </c>
-      <c r="H11" s="46" t="s">
+      <c r="H11" s="32" t="s">
         <v>377</v>
       </c>
-      <c r="I11" s="46" t="s">
+      <c r="I11" s="32" t="s">
         <v>378</v>
       </c>
-      <c r="J11" s="46" t="s">
+      <c r="J11" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="K11" s="46" t="s">
+      <c r="K11" s="32" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="30" t="s">
         <v>381</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="I12" s="22" t="s">
+      <c r="I12" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="J12" s="22" t="s">
+      <c r="J12" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="K12" s="22" t="s">
+      <c r="K12" s="3" t="s">
         <v>391</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="B4:C4"/>
@@ -6175,6 +6174,11 @@
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="J4:K4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6191,337 +6195,332 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="37" t="s">
         <v>392</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="38" t="s">
         <v>393</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="24" t="s">
         <v>303</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="50" t="s">
         <v>304</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="50"/>
+      <c r="D4" s="51" t="s">
         <v>305</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="51" t="s">
+      <c r="E4" s="51"/>
+      <c r="F4" s="52" t="s">
         <v>306</v>
       </c>
-      <c r="G4" s="51"/>
-      <c r="H4" s="52" t="s">
+      <c r="G4" s="52"/>
+      <c r="H4" s="53" t="s">
         <v>307</v>
       </c>
-      <c r="I4" s="52"/>
-      <c r="J4" s="53" t="s">
+      <c r="I4" s="53"/>
+      <c r="J4" s="54" t="s">
         <v>308</v>
       </c>
-      <c r="K4" s="53"/>
+      <c r="K4" s="54"/>
     </row>
     <row r="5" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="24" t="s">
         <v>309</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="25" t="s">
         <v>310</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="25" t="s">
         <v>311</v>
       </c>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="26" t="s">
         <v>312</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="F5" s="41" t="s">
+      <c r="F5" s="27" t="s">
         <v>314</v>
       </c>
-      <c r="G5" s="41" t="s">
+      <c r="G5" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="H5" s="42" t="s">
+      <c r="H5" s="28" t="s">
         <v>316</v>
       </c>
-      <c r="I5" s="42" t="s">
+      <c r="I5" s="28" t="s">
         <v>317</v>
       </c>
-      <c r="J5" s="43" t="s">
+      <c r="J5" s="29" t="s">
         <v>318</v>
       </c>
-      <c r="K5" s="43" t="s">
+      <c r="K5" s="29" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="30" t="s">
         <v>320</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="49" t="s">
         <v>394</v>
       </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54" t="s">
+      <c r="C6" s="49"/>
+      <c r="D6" s="49" t="s">
         <v>395</v>
       </c>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54" t="s">
+      <c r="E6" s="49"/>
+      <c r="F6" s="49" t="s">
         <v>396</v>
       </c>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54" t="s">
+      <c r="G6" s="49"/>
+      <c r="H6" s="49" t="s">
         <v>397</v>
       </c>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54" t="s">
+      <c r="I6" s="49"/>
+      <c r="J6" s="49" t="s">
         <v>398</v>
       </c>
-      <c r="K6" s="54"/>
+      <c r="K6" s="49"/>
     </row>
     <row r="7" spans="1:11" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="30" t="s">
         <v>399</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="I7" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="J7" s="17" t="s">
+      <c r="J7" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="K7" s="17" t="s">
+      <c r="K7" s="2" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="30" t="s">
         <v>337</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="H8" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="I8" s="17" t="s">
+      <c r="I8" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="J8" s="17" t="s">
+      <c r="J8" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="K8" s="17" t="s">
+      <c r="K8" s="2" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="30" t="s">
         <v>420</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="G9" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="H9" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="I9" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="J9" s="17" t="s">
+      <c r="J9" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="K9" s="17" t="s">
+      <c r="K9" s="2" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="30" t="s">
         <v>431</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="32" t="s">
         <v>432</v>
       </c>
-      <c r="C10" s="46" t="s">
+      <c r="C10" s="32" t="s">
         <v>433</v>
       </c>
-      <c r="D10" s="46" t="s">
+      <c r="D10" s="32" t="s">
         <v>434</v>
       </c>
-      <c r="E10" s="46" t="s">
+      <c r="E10" s="32" t="s">
         <v>435</v>
       </c>
-      <c r="F10" s="46" t="s">
+      <c r="F10" s="32" t="s">
         <v>375</v>
       </c>
-      <c r="G10" s="46" t="s">
+      <c r="G10" s="32" t="s">
         <v>436</v>
       </c>
-      <c r="H10" s="46" t="s">
+      <c r="H10" s="32" t="s">
         <v>437</v>
       </c>
-      <c r="I10" s="46" t="s">
+      <c r="I10" s="32" t="s">
         <v>438</v>
       </c>
-      <c r="J10" s="46" t="s">
+      <c r="J10" s="32" t="s">
         <v>439</v>
       </c>
-      <c r="K10" s="46" t="s">
+      <c r="K10" s="32" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="30" t="s">
         <v>441</v>
       </c>
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="33" t="s">
         <v>442</v>
       </c>
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="33" t="s">
         <v>443</v>
       </c>
-      <c r="D11" s="47" t="s">
+      <c r="D11" s="33" t="s">
         <v>444</v>
       </c>
-      <c r="E11" s="47" t="s">
+      <c r="E11" s="33" t="s">
         <v>445</v>
       </c>
-      <c r="F11" s="47" t="s">
+      <c r="F11" s="33" t="s">
         <v>446</v>
       </c>
-      <c r="G11" s="47" t="s">
+      <c r="G11" s="33" t="s">
         <v>447</v>
       </c>
-      <c r="H11" s="47" t="s">
+      <c r="H11" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="I11" s="47" t="s">
+      <c r="I11" s="33" t="s">
         <v>449</v>
       </c>
-      <c r="J11" s="47" t="s">
+      <c r="J11" s="33" t="s">
         <v>450</v>
       </c>
-      <c r="K11" s="47" t="s">
+      <c r="K11" s="33" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="30" t="s">
         <v>452</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="I12" s="22" t="s">
+      <c r="I12" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="J12" s="22" t="s">
+      <c r="J12" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="K12" s="22" t="s">
+      <c r="K12" s="3" t="s">
         <v>461</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="B4:C4"/>
@@ -6529,6 +6528,11 @@
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="J4:K4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6545,162 +6549,162 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="37" t="s">
         <v>462</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="38" t="s">
         <v>463</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="24" t="s">
         <v>303</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="50" t="s">
         <v>304</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="50"/>
+      <c r="D4" s="51" t="s">
         <v>305</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="51" t="s">
+      <c r="E4" s="51"/>
+      <c r="F4" s="52" t="s">
         <v>306</v>
       </c>
-      <c r="G4" s="51"/>
-      <c r="H4" s="52" t="s">
+      <c r="G4" s="52"/>
+      <c r="H4" s="53" t="s">
         <v>307</v>
       </c>
-      <c r="I4" s="52"/>
-      <c r="J4" s="53" t="s">
+      <c r="I4" s="53"/>
+      <c r="J4" s="54" t="s">
         <v>308</v>
       </c>
-      <c r="K4" s="53"/>
+      <c r="K4" s="54"/>
     </row>
     <row r="5" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="24" t="s">
         <v>309</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="25" t="s">
         <v>310</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="25" t="s">
         <v>311</v>
       </c>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="26" t="s">
         <v>312</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="F5" s="41" t="s">
+      <c r="F5" s="27" t="s">
         <v>314</v>
       </c>
-      <c r="G5" s="41" t="s">
+      <c r="G5" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="H5" s="42" t="s">
+      <c r="H5" s="28" t="s">
         <v>316</v>
       </c>
-      <c r="I5" s="42" t="s">
+      <c r="I5" s="28" t="s">
         <v>317</v>
       </c>
-      <c r="J5" s="43" t="s">
+      <c r="J5" s="29" t="s">
         <v>318</v>
       </c>
-      <c r="K5" s="43" t="s">
+      <c r="K5" s="29" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="30" t="s">
         <v>464</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="I6" s="17" t="s">
+      <c r="I6" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="J6" s="17" t="s">
+      <c r="J6" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="K6" s="17" t="s">
+      <c r="K6" s="2" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="30" t="s">
         <v>337</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="I7" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="J7" s="17" t="s">
+      <c r="J7" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="K7" s="17" t="s">
+      <c r="K7" s="2" t="s">
         <v>347</v>
       </c>
     </row>
@@ -6720,37 +6724,37 @@
       <c r="K8" s="55"/>
     </row>
     <row r="9" spans="1:11" ht="84.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="30" t="s">
         <v>476</v>
       </c>
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="34" t="s">
         <v>477</v>
       </c>
-      <c r="C9" s="48" t="s">
+      <c r="C9" s="34" t="s">
         <v>478</v>
       </c>
-      <c r="D9" s="48" t="s">
+      <c r="D9" s="34" t="s">
         <v>479</v>
       </c>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="34" t="s">
         <v>480</v>
       </c>
-      <c r="F9" s="48" t="s">
+      <c r="F9" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="G9" s="48" t="s">
+      <c r="G9" s="34" t="s">
         <v>482</v>
       </c>
-      <c r="H9" s="48" t="s">
+      <c r="H9" s="34" t="s">
         <v>483</v>
       </c>
-      <c r="I9" s="48" t="s">
+      <c r="I9" s="34" t="s">
         <v>484</v>
       </c>
-      <c r="J9" s="48" t="s">
+      <c r="J9" s="34" t="s">
         <v>485</v>
       </c>
-      <c r="K9" s="48" t="s">
+      <c r="K9" s="34" t="s">
         <v>486</v>
       </c>
     </row>
@@ -6770,37 +6774,37 @@
       <c r="K10" s="55"/>
     </row>
     <row r="11" spans="1:11" ht="84.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="30" t="s">
         <v>488</v>
       </c>
-      <c r="B11" s="49" t="s">
+      <c r="B11" s="35" t="s">
         <v>489</v>
       </c>
-      <c r="C11" s="49" t="s">
+      <c r="C11" s="35" t="s">
         <v>490</v>
       </c>
-      <c r="D11" s="49" t="s">
+      <c r="D11" s="35" t="s">
         <v>491</v>
       </c>
-      <c r="E11" s="49" t="s">
+      <c r="E11" s="35" t="s">
         <v>492</v>
       </c>
-      <c r="F11" s="49" t="s">
+      <c r="F11" s="35" t="s">
         <v>493</v>
       </c>
-      <c r="G11" s="49" t="s">
+      <c r="G11" s="35" t="s">
         <v>494</v>
       </c>
-      <c r="H11" s="49" t="s">
+      <c r="H11" s="35" t="s">
         <v>495</v>
       </c>
-      <c r="I11" s="49" t="s">
+      <c r="I11" s="35" t="s">
         <v>496</v>
       </c>
-      <c r="J11" s="49" t="s">
+      <c r="J11" s="35" t="s">
         <v>497</v>
       </c>
-      <c r="K11" s="49" t="s">
+      <c r="K11" s="35" t="s">
         <v>498</v>
       </c>
     </row>
@@ -6820,89 +6824,89 @@
       <c r="K12" s="55"/>
     </row>
     <row r="13" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="44" t="s">
+      <c r="A13" s="30" t="s">
         <v>500</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="F13" s="17" t="s">
+      <c r="F13" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="G13" s="17" t="s">
+      <c r="G13" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="H13" s="17" t="s">
+      <c r="H13" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="I13" s="17" t="s">
+      <c r="I13" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="J13" s="17" t="s">
+      <c r="J13" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="K13" s="17" t="s">
+      <c r="K13" s="2" t="s">
         <v>509</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="84.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="44" t="s">
+      <c r="A14" s="30" t="s">
         <v>510</v>
       </c>
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="31" t="s">
         <v>511</v>
       </c>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="31" t="s">
         <v>512</v>
       </c>
-      <c r="D14" s="45" t="s">
+      <c r="D14" s="31" t="s">
         <v>513</v>
       </c>
-      <c r="E14" s="45" t="s">
+      <c r="E14" s="31" t="s">
         <v>514</v>
       </c>
-      <c r="F14" s="45" t="s">
+      <c r="F14" s="31" t="s">
         <v>515</v>
       </c>
-      <c r="G14" s="45" t="s">
+      <c r="G14" s="31" t="s">
         <v>516</v>
       </c>
-      <c r="H14" s="45" t="s">
+      <c r="H14" s="31" t="s">
         <v>517</v>
       </c>
-      <c r="I14" s="45" t="s">
+      <c r="I14" s="31" t="s">
         <v>518</v>
       </c>
-      <c r="J14" s="45" t="s">
+      <c r="J14" s="31" t="s">
         <v>519</v>
       </c>
-      <c r="K14" s="45" t="s">
+      <c r="K14" s="31" t="s">
         <v>520</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="39" t="s">
         <v>521</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -6935,142 +6939,142 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="37" t="s">
         <v>522</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="38" t="s">
         <v>523</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
     </row>
     <row r="4" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="1" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="24">
+      <c r="A5" s="10">
         <v>1</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D5" s="10" t="s">
         <v>530</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="14" t="s">
         <v>531</v>
       </c>
-      <c r="F5" s="50" t="s">
+      <c r="F5" s="36" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="24">
+      <c r="A6" s="10">
         <v>2</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="10" t="s">
         <v>534</v>
       </c>
-      <c r="E6" s="28" t="s">
+      <c r="E6" s="14" t="s">
         <v>531</v>
       </c>
-      <c r="F6" s="50" t="s">
+      <c r="F6" s="36" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="24">
+      <c r="A7" s="10">
         <v>3</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="10" t="s">
         <v>537</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="14" t="s">
         <v>531</v>
       </c>
-      <c r="F7" s="50" t="s">
+      <c r="F7" s="36" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="24">
+      <c r="A8" s="10">
         <v>4</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="10" t="s">
         <v>539</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="50" t="s">
+      <c r="F8" s="36" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="24">
+      <c r="A9" s="10">
         <v>5</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="10" t="s">
         <v>537</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="14" t="s">
         <v>531</v>
       </c>
-      <c r="F9" s="50" t="s">
+      <c r="F9" s="36" t="s">
         <v>535</v>
       </c>
     </row>
